--- a/Result/profitability/3021.xlsx
+++ b/Result/profitability/3021.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.03</v>
       </c>
       <c r="M2" t="n">
-        <v>0.08375</v>
+        <v>0.09125000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>18.46125</v>
+        <v>18.84625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.06625</v>
+        <v>0.11</v>
       </c>
       <c r="N3" t="n">
-        <v>20.98125</v>
+        <v>21.75625</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.23</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0475</v>
+        <v>0.08875</v>
       </c>
       <c r="N4" t="n">
-        <v>22.5775</v>
+        <v>23.355</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.17</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07625000000000001</v>
+        <v>0.09875</v>
       </c>
       <c r="N5" t="n">
-        <v>23.535</v>
+        <v>24.15125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>-0.64</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.01499999999999999</v>
+        <v>-0.035</v>
       </c>
       <c r="N6" t="n">
-        <v>20.635</v>
+        <v>20.89375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.06874999999999999</v>
+        <v>-0.01749999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>21.96125</v>
+        <v>22.8425</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.18</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.02874999999999999</v>
+        <v>-0.01875</v>
       </c>
       <c r="N8" t="n">
-        <v>23.34625</v>
+        <v>23.4925</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1520,7 +1520,7 @@
         <v>0.45</v>
       </c>
       <c r="M9" t="n">
-        <v>0.00375000000000001</v>
+        <v>0.003750000000000003</v>
       </c>
       <c r="N9" t="n">
         <v>23.3675</v>
@@ -1647,7 +1647,7 @@
         <v>0.04</v>
       </c>
       <c r="M10" t="n">
-        <v>0.005000000000000011</v>
+        <v>0.005000000000000004</v>
       </c>
       <c r="N10" t="n">
         <v>22.4025</v>
@@ -1774,7 +1774,7 @@
         <v>0.22</v>
       </c>
       <c r="M11" t="n">
-        <v>0.02375000000000001</v>
+        <v>0.02375</v>
       </c>
       <c r="N11" t="n">
         <v>21.12</v>
@@ -1903,7 +1903,7 @@
         <v>0.06</v>
       </c>
       <c r="M12" t="n">
-        <v>0.06000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="N12" t="n">
         <v>20.7575</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3021</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>766</v>
+      </c>
+      <c r="D75" t="n">
+        <v>608</v>
+      </c>
+      <c r="E75" t="n">
+        <v>158</v>
+      </c>
+      <c r="F75" t="n">
+        <v>20.59</v>
+      </c>
+      <c r="G75" t="n">
+        <v>55</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>7.15%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>50</v>
+      </c>
+      <c r="K75" t="n">
+        <v>26</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.11375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.08000000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.4210526315789473</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.169999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.06024716786817708</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.3148148148148149</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
